--- a/uploads/a3afbe10-7a22-44d7-8428-9e67fa4947a4/materials_summary.xlsx
+++ b/uploads/a3afbe10-7a22-44d7-8428-9e67fa4947a4/materials_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сводка по материалам" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка по материалам" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8222.279</v>
+        <v>30.83</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1298</v>
+        <v>73</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>54</v>
@@ -560,7 +560,139 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>расчёт по объёму (1298 эл.) + 54 эл. по количеству</t>
+          <t>расчёт по объёму (73 эл.) + 54 эл. по количеству</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Бетон В10</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Бетон</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>В10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>266.561</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>расчёт по объёму (8 эл.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Бетон В25</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Бетон</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>В25</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2269.207</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>расчёт по объёму (66 эл.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Бетон В30</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Бетон</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>В30</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3931.077</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1037</v>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>расчёт по объёму (1037 эл.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Бетон В35</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Бетон</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>В35</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1755.07</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>расчёт по объёму (186 эл.)</t>
         </is>
       </c>
     </row>
